--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -744,7 +744,7 @@
         <v>200000</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -758,7 +758,7 @@
         <v/>
       </c>
       <c r="J8" t="n">
-        <v>270000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="9">

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -744,7 +744,7 @@
         <v>200000</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -758,7 +758,7 @@
         <v/>
       </c>
       <c r="J8" t="n">
-        <v>300000</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="9">

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -744,7 +744,7 @@
         <v>200000</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -758,7 +758,7 @@
         <v/>
       </c>
       <c r="J8" t="n">
-        <v>270000</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="9">

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -744,7 +744,7 @@
         <v>200000</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -758,7 +758,7 @@
         <v/>
       </c>
       <c r="J8" t="n">
-        <v>360000</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="9">

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -744,7 +744,7 @@
         <v>200000</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -758,7 +758,7 @@
         <v/>
       </c>
       <c r="J8" t="n">
-        <v>270000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="9">

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -744,7 +744,7 @@
         <v>200000</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -758,7 +758,7 @@
         <v/>
       </c>
       <c r="J8" t="n">
-        <v>750000</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="9">

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>2222</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>2222</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -664,7 +664,7 @@
         <v>200000</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>47777</v>
       </c>
       <c r="G6" t="n">
         <v>4</v>
@@ -678,7 +678,7 @@
         <v/>
       </c>
       <c r="J6" t="n">
-        <v>140000</v>
+        <v>1672195000</v>
       </c>
     </row>
     <row r="7">

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -664,7 +664,7 @@
         <v>200000</v>
       </c>
       <c r="F6" t="n">
-        <v>47777</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>4</v>
@@ -678,7 +678,7 @@
         <v/>
       </c>
       <c r="J6" t="n">
-        <v>1672195000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="7">

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -584,7 +584,7 @@
         <v>100000</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>47777</v>
       </c>
       <c r="G4" t="n">
         <v>31</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>27777</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>
@@ -584,7 +584,7 @@
         <v>100000</v>
       </c>
       <c r="F4" t="n">
-        <v>47777</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>31</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>27777</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>2777</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>2777</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>277</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>277</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -544,7 +544,7 @@
         <v>100000</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>477</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -544,7 +544,7 @@
         <v>100000</v>
       </c>
       <c r="F3" t="n">
-        <v>477</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>23333</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>23333</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>233</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>233</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -504,7 +504,7 @@
         <v>100000</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>
